--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_3_12.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_3_12.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319439.7096585986</v>
+        <v>299468.8733437747</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>3013503.893776012</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745724</v>
+        <v>20373567.14494818</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4813416.085193353</v>
+        <v>4790050.627124563</v>
       </c>
     </row>
     <row r="11">
@@ -1174,16 +1174,16 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>19.82224313344393</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1448,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1557,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1755,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>22.54368386855027</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>14.67170078545518</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1922,19 +1922,19 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>23.91580867374213</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2034,22 +2034,22 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>234.2620311992098</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2116,22 +2116,22 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>102.3382270926889</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>70.68340629747387</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2204,19 +2204,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>114.9211591858873</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2229,13 +2229,13 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2308,25 +2308,25 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2396,19 +2396,19 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>23.17000630062659</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>203.3816115706753</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>21.18375537072436</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>3.252730413754582</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>38.68263444269184</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>68.67434453202564</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>190.3453970742847</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2800,10 +2800,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>112.2877629084735</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2824,16 +2824,16 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2842,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2858,28 +2858,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>84.41990506940002</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2906,28 +2906,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>49.23175083062952</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2949,55 +2949,55 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3031,10 +3031,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -3095,31 +3095,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>4.586460976949843</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3146,10 +3146,10 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>117.0178591544169</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3253,31 +3253,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>71.01467844038818</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3298,16 +3298,16 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>38.32399625825719</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>89.93607067950306</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>232.8330857361503</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3538,16 +3538,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>29.51218284430547</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="39">
@@ -3584,16 +3584,16 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>55.26115413364287</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>198.5990147965224</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3705,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>187.9840913941556</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3787,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>124.0090888823614</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3854,28 +3854,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>16.58531419226327</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="Y43" t="n">
-        <v>47.02492433367365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82000000000018</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56000000000017</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.30000000000017</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348994</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994383</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.62772033681205</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>48.36509407418578</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>22.10246781155952</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>101.2510699645389</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.98844370191262</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>48.72581743928635</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>22.46319117666009</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80.86787878787879</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54.60525252525252</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>28.34262626262626</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>26.78000000000001</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>29.96</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="N17" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>73.62555634894463</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S17" t="n">
-        <v>45.34272806611634</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T17" t="n">
-        <v>17.05989978328806</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="U17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.05989978328806</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>31.276960935614</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.994132652785714</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>28.84</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N18" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="S19" t="n">
-        <v>52.76774507695567</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="T19" t="n">
-        <v>52.76774507695567</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="U19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="V19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="X19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>52.75142891054807</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S20" t="n">
-        <v>742.7770012113231</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T20" t="n">
-        <v>742.7770012113231</v>
+        <v>366.1018663125844</v>
       </c>
       <c r="U20" t="n">
-        <v>499.3426577769796</v>
+        <v>122.6530896684844</v>
       </c>
       <c r="V20" t="n">
-        <v>499.3426577769796</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W20" t="n">
-        <v>255.9083143426362</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X20" t="n">
-        <v>255.9083143426362</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y20" t="n">
-        <v>255.9083143426362</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>90.67738009845846</v>
+        <v>194.4883050441255</v>
       </c>
       <c r="C21" t="n">
-        <v>90.67738009845846</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N21" t="n">
-        <v>781.3565223866492</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>761.813405358766</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>533.5897870951551</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V21" t="n">
-        <v>298.4376788634124</v>
+        <v>645.7885818937584</v>
       </c>
       <c r="W21" t="n">
-        <v>298.4376788634124</v>
+        <v>402.3398052496583</v>
       </c>
       <c r="X21" t="n">
-        <v>298.4376788634124</v>
+        <v>194.4883050441255</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.67738009845846</v>
+        <v>194.4883050441255</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C23" t="n">
-        <v>962.184938960006</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D23" t="n">
-        <v>962.184938960006</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E23" t="n">
-        <v>718.7505955256626</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y23" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>385.8377695737441</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C24" t="n">
-        <v>385.8377695737441</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D24" t="n">
-        <v>385.8377695737441</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E24" t="n">
-        <v>385.8377695737441</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F24" t="n">
-        <v>362.4337228054344</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>223.7028973880499</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3337617956292</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M24" t="n">
-        <v>234.7819638733197</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N24" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T24" t="n">
-        <v>761.813405358766</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U24" t="n">
-        <v>761.813405358766</v>
+        <v>432.4774131586771</v>
       </c>
       <c r="V24" t="n">
-        <v>761.813405358766</v>
+        <v>432.4774131586771</v>
       </c>
       <c r="W24" t="n">
-        <v>761.813405358766</v>
+        <v>432.4774131586771</v>
       </c>
       <c r="X24" t="n">
-        <v>761.813405358766</v>
+        <v>227.0414418751666</v>
       </c>
       <c r="Y24" t="n">
-        <v>554.0531065938121</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>752.8686165795501</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T26" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U26" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V26" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="W26" t="n">
-        <v>749.5830303030303</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="X26" t="n">
-        <v>506.1486868686869</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="Y26" t="n">
-        <v>506.1486868686869</v>
+        <v>527.5764290961142</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>319.0111943422526</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="C27" t="n">
-        <v>319.0111943422526</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="D27" t="n">
-        <v>319.0111943422526</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="E27" t="n">
-        <v>319.0111943422526</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="F27" t="n">
-        <v>172.4766363691375</v>
+        <v>271.3811041200179</v>
       </c>
       <c r="G27" t="n">
-        <v>133.4032682452064</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>487.8331058683492</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N27" t="n">
-        <v>726.4231058683491</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U27" t="n">
-        <v>487.2265313623206</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="V27" t="n">
-        <v>487.2265313623206</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="W27" t="n">
-        <v>487.2265313623206</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="X27" t="n">
-        <v>487.2265313623206</v>
+        <v>417.9156620931329</v>
       </c>
       <c r="Y27" t="n">
-        <v>487.2265313623206</v>
+        <v>417.9156620931329</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>132.7019827358318</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="C29" t="n">
-        <v>132.7019827358318</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D29" t="n">
-        <v>132.7019827358318</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E29" t="n">
-        <v>132.7019827358318</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F29" t="n">
-        <v>132.7019827358318</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G29" t="n">
-        <v>132.7019827358318</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H29" t="n">
-        <v>132.7019827358318</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>812.6170525846973</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S29" t="n">
-        <v>601.4856691642474</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T29" t="n">
-        <v>376.1363261701753</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U29" t="n">
-        <v>376.1363261701753</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V29" t="n">
-        <v>376.1363261701753</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W29" t="n">
-        <v>376.1363261701753</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X29" t="n">
-        <v>132.7019827358318</v>
+        <v>467.067986854209</v>
       </c>
       <c r="Y29" t="n">
-        <v>132.7019827358318</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>500.6242735046464</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C30" t="n">
-        <v>500.6242735046464</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D30" t="n">
-        <v>500.6242735046464</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E30" t="n">
-        <v>341.3868184991909</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F30" t="n">
-        <v>194.8522605260759</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G30" t="n">
-        <v>194.8522605260759</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>109.5796291428435</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>711.9619638733197</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O30" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>813.1585848204618</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>813.1585848204618</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>813.1585848204618</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>813.1585848204618</v>
       </c>
       <c r="W30" t="n">
-        <v>500.6242735046464</v>
+        <v>569.7098081763618</v>
       </c>
       <c r="X30" t="n">
-        <v>500.6242735046464</v>
+        <v>569.7098081763618</v>
       </c>
       <c r="Y30" t="n">
-        <v>500.6242735046464</v>
+        <v>361.9495094114078</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E32" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>668.7151515151515</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>451.5434343434343</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W32" t="n">
-        <v>234.3717171717172</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X32" t="n">
-        <v>234.3717171717172</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="Y32" t="n">
-        <v>234.3717171717172</v>
+        <v>477.1596022224361</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>192.4071619339127</v>
+        <v>512.8480801015824</v>
       </c>
       <c r="C33" t="n">
-        <v>17.95413265278571</v>
+        <v>512.8480801015824</v>
       </c>
       <c r="D33" t="n">
-        <v>17.95413265278571</v>
+        <v>512.8480801015824</v>
       </c>
       <c r="E33" t="n">
-        <v>17.95413265278571</v>
+        <v>508.2152912359765</v>
       </c>
       <c r="F33" t="n">
-        <v>17.95413265278571</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G33" t="n">
-        <v>17.95413265278571</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H33" t="n">
-        <v>17.95413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M33" t="n">
-        <v>355.4075600578374</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N33" t="n">
-        <v>568.2575600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O33" t="n">
-        <v>781.1075600578374</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P33" t="n">
-        <v>790.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>686.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T33" t="n">
-        <v>568.3827977189346</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U33" t="n">
-        <v>568.3827977189346</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V33" t="n">
-        <v>568.3827977189346</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W33" t="n">
-        <v>568.3827977189346</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X33" t="n">
-        <v>568.3827977189346</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y33" t="n">
-        <v>360.6224989539808</v>
+        <v>512.8480801015824</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>234.3717171717172</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T35" t="n">
-        <v>668.7151515151515</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U35" t="n">
-        <v>668.7151515151515</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V35" t="n">
-        <v>668.7151515151515</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W35" t="n">
-        <v>668.7151515151515</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X35" t="n">
-        <v>451.5434343434343</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="Y35" t="n">
-        <v>451.5434343434343</v>
+        <v>802.5825927271064</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>338.9417199070277</v>
+        <v>168.215552771464</v>
       </c>
       <c r="C36" t="n">
-        <v>164.4886906259007</v>
+        <v>168.215552771464</v>
       </c>
       <c r="D36" t="n">
-        <v>164.4886906259007</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>164.4886906259007</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>230.05</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M36" t="n">
-        <v>442.9</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N36" t="n">
-        <v>647.15</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>758.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S36" t="n">
-        <v>585.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T36" t="n">
-        <v>585.4131260035546</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U36" t="n">
-        <v>585.4131260035546</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V36" t="n">
-        <v>585.4131260035546</v>
+        <v>168.215552771464</v>
       </c>
       <c r="W36" t="n">
-        <v>585.4131260035546</v>
+        <v>168.215552771464</v>
       </c>
       <c r="X36" t="n">
-        <v>585.4131260035546</v>
+        <v>168.215552771464</v>
       </c>
       <c r="Y36" t="n">
-        <v>377.6528272386007</v>
+        <v>168.215552771464</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>234.3717171717172</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="C38" t="n">
-        <v>234.3717171717172</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="D38" t="n">
-        <v>17.2</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="E38" t="n">
-        <v>17.2</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>698.5254372164702</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S38" t="n">
-        <v>668.7151515151515</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T38" t="n">
-        <v>451.5434343434343</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U38" t="n">
-        <v>234.3717171717172</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V38" t="n">
-        <v>234.3717171717172</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W38" t="n">
-        <v>234.3717171717172</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X38" t="n">
-        <v>234.3717171717172</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y38" t="n">
-        <v>234.3717171717172</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>142.5575600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>251.6565223866492</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N39" t="n">
-        <v>464.5065223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O39" t="n">
-        <v>677.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T39" t="n">
-        <v>860</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U39" t="n">
-        <v>860</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="V39" t="n">
-        <v>642.8282828282828</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="W39" t="n">
-        <v>425.6565656565656</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="X39" t="n">
-        <v>217.8050654510328</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>279.5233881080029</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>17.2</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>232.1915151515151</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="C41" t="n">
-        <v>232.1915151515151</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="D41" t="n">
-        <v>232.1915151515151</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="E41" t="n">
-        <v>232.1915151515151</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>196.4204723580617</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="T41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="U41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="V41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="W41" t="n">
-        <v>421.6969696969697</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="X41" t="n">
-        <v>421.6969696969697</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="Y41" t="n">
-        <v>421.6969696969697</v>
+        <v>663.8141338692145</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="C42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="D42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="E42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="F42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.82807374217315</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>390.368997361522</v>
       </c>
       <c r="N42" t="n">
-        <v>599.9619638733197</v>
+        <v>390.368997361522</v>
       </c>
       <c r="O42" t="n">
-        <v>599.9619638733197</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="S42" t="n">
-        <v>678.5826554506689</v>
+        <v>579.1101804729262</v>
       </c>
       <c r="T42" t="n">
-        <v>678.5826554506689</v>
+        <v>562.3573378544785</v>
       </c>
       <c r="U42" t="n">
-        <v>678.5826554506689</v>
+        <v>562.3573378544785</v>
       </c>
       <c r="V42" t="n">
-        <v>678.5826554506689</v>
+        <v>346.7772735945362</v>
       </c>
       <c r="W42" t="n">
-        <v>463.4311402991538</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="X42" t="n">
-        <v>463.4311402991538</v>
+        <v>131.1972093345938</v>
       </c>
       <c r="Y42" t="n">
-        <v>255.6708415341998</v>
+        <v>131.1972093345938</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>746.4788889868139</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>785.6669271790361</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>829.3577778344724</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="V43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="W43" t="n">
-        <v>64.53992356936732</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="X43" t="n">
-        <v>64.53992356936732</v>
+        <v>719.1647639791009</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>719.1647639791009</v>
       </c>
     </row>
     <row r="44">
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
         <v>235.7664149699872</v>
@@ -8442,13 +8442,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8515,10 +8515,10 @@
         <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>163.5038747293692</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
@@ -8527,10 +8527,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812385</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,16 +8670,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
         <v>230.0982114216867</v>
@@ -8749,19 +8749,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
         <v>133.9744074143302</v>
@@ -8831,16 +8831,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>135.0065633140411</v>
@@ -8907,16 +8907,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>254.3625585460859</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
         <v>230.0982114216867</v>
@@ -8992,19 +8992,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,16 +9068,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>135.0065633140411</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7664149699872</v>
+        <v>262.2416917349371</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>165.4314642346751</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>169.0027207907052</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>157.8169888482831</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>167.5717993463377</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9393,7 +9393,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O20" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
         <v>321.7987081714826</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444444</v>
+        <v>312.5053919605859</v>
       </c>
       <c r="P21" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>359.81278530921</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,22 +9934,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>301.248502863135</v>
       </c>
       <c r="O27" t="n">
-        <v>382.5729051834858</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10092,10 +10092,10 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M29" t="n">
         <v>449.5135334928325</v>
@@ -10171,25 +10171,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>357.73449794694</v>
+        <v>244.7225752110828</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10408,22 +10408,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>143.5682270394143</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
         <v>210.0772877358491</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10648,16 +10648,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>353.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N36" t="n">
-        <v>337.6548433964646</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10882,22 +10882,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>252.3350059713231</v>
+        <v>382.1386950879875</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.1454125711647</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
-        <v>312.9032497650775</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11122,16 +11122,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>179.1516856726523</v>
       </c>
       <c r="N42" t="n">
-        <v>167.5279785636185</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
@@ -23032,16 +23032,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>326.340168717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
         <v>369.731100678469</v>
@@ -23057,13 +23057,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>149.8076989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>121.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
         <v>157.6450804554009</v>
@@ -23120,7 +23120,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
-        <v>208.1233462948376</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23215,10 +23215,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>356.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C11" t="n">
-        <v>339.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D11" t="n">
         <v>354.683041620683</v>
@@ -23275,7 +23275,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
-        <v>304.8514584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23284,7 +23284,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y11" t="n">
-        <v>360.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="12">
@@ -23306,10 +23306,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>122.1684123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
         <v>112.2354442364965</v>
@@ -23357,10 +23357,10 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X12" t="n">
-        <v>179.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
         <v>205.6826957773044</v>
@@ -23415,19 +23415,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
-        <v>151.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S13" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T13" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U13" t="n">
         <v>286.3190293564909</v>
@@ -23452,16 +23452,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>359.8330416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
-        <v>339.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
-        <v>328.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>355.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
         <v>406.8760457417114</v>
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>140.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>146.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>124.5442655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
         <v>157.6450804554009</v>
@@ -23600,7 +23600,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y15" t="n">
-        <v>179.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="16">
@@ -23613,16 +23613,16 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C16" t="n">
-        <v>141.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D16" t="n">
-        <v>122.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E16" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F16" t="n">
-        <v>122.877364154381</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
         <v>167.9909793584588</v>
@@ -23655,7 +23655,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>60.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
         <v>177.2933913771695</v>
@@ -23710,7 +23710,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I17" t="n">
-        <v>195.8041887849507</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>122.2790926808335</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0200695862453</v>
+        <v>181.4300443259292</v>
       </c>
       <c r="T17" t="n">
-        <v>195.0958495641314</v>
+        <v>198.7945553148449</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>223.7556276475204</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23780,19 +23780,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>117.0692123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>109.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>88.31963556275433</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I18" t="n">
-        <v>61.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23865,10 +23865,10 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H19" t="n">
-        <v>162.2271725074396</v>
+        <v>139.7784131469302</v>
       </c>
       <c r="I19" t="n">
-        <v>155.4504749272583</v>
+        <v>127.8604496669421</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
@@ -23892,22 +23892,22 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>149.7033661168533</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
-        <v>230.1151756976419</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>148.4718104642707</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
@@ -23974,22 +23974,22 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V20" t="n">
-        <v>327.7522584701349</v>
+        <v>225.414031377446</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
@@ -24008,10 +24008,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>76.76165926716489</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
@@ -24029,7 +24029,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24062,19 +24062,19 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>117.8794279635379</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24087,13 +24087,13 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325984</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
-        <v>13.24699506120115</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F22" t="n">
         <v>145.4210480229312</v>
@@ -24166,25 +24166,25 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>365.2728917710076</v>
+        <v>152.9875061275656</v>
       </c>
       <c r="D23" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -24232,7 +24232,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>384.4410282264595</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24242,7 +24242,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
         <v>172.7084989883157</v>
@@ -24254,19 +24254,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>121.8992060927573</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24290,7 +24290,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>171.6831711038378</v>
@@ -24299,7 +24299,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24308,7 +24308,7 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>2.391373632802186</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>179.8319801819373</v>
+        <v>46.6450125965693</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24372,7 +24372,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
@@ -24400,13 +24400,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141.7338416634806</v>
+        <v>361.5500862927562</v>
       </c>
       <c r="C26" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D26" t="n">
-        <v>113.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E26" t="n">
         <v>381.9303700722618</v>
@@ -24454,7 +24454,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>219.8431191503768</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>251.3456529078365</v>
@@ -24466,7 +24466,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24494,7 +24494,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>98.6608827205188</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -24503,7 +24503,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24536,7 +24536,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>157.2670375489492</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24570,13 +24570,13 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F28" t="n">
-        <v>12.23408043756322</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
         <v>167.9909793584588</v>
       </c>
       <c r="H28" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I28" t="n">
         <v>155.4504749272583</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>192.3884445891959</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24658,10 +24658,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
-        <v>98.18812666193242</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,16 +24682,16 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
         <v>251.3456529078365</v>
@@ -24700,10 +24700,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24716,28 +24716,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>27.81553916709643</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -24764,28 +24764,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>122.4514202732083</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24807,7 +24807,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F31" t="n">
-        <v>12.23408043756322</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
         <v>167.9909793584588</v>
@@ -24855,7 +24855,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W31" t="n">
         <v>286.522998336591</v>
@@ -24874,7 +24874,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
         <v>365.2728917710076</v>
@@ -24889,10 +24889,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
-        <v>339.4748021157671</v>
+        <v>127.189416472325</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24931,16 +24931,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>61.97365290783654</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>112.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>134.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y32" t="n">
         <v>386.2379386560536</v>
@@ -24953,31 +24953,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>153.0586194784511</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25004,10 +25004,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>83.14686954040469</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
         <v>225.9413820809748</v>
@@ -25016,7 +25016,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25083,7 +25083,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T34" t="n">
         <v>227.9455894282815</v>
@@ -25101,7 +25101,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y34" t="n">
-        <v>85.39768576672674</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="35">
@@ -25111,31 +25111,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>406.8760457417114</v>
+        <v>335.8613673013232</v>
       </c>
       <c r="G35" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I35" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25156,16 +25156,16 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>33.7238495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
         <v>251.3456529078365</v>
@@ -25177,7 +25177,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>154.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>128.2091873916102</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25244,13 +25244,13 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>142.8645164699222</v>
       </c>
       <c r="W36" t="n">
         <v>251.6949831609196</v>
@@ -25259,7 +25259,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -25329,7 +25329,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>118.9506757384599</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,13 +25348,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>149.9007559273302</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
         <v>381.9303700722618</v>
@@ -25369,7 +25369,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>179.5078867419399</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>36.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="39">
@@ -25442,16 +25442,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>82.08236302956777</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>7.083680980781907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25563,10 +25563,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711228</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W40" t="n">
         <v>286.522998336591</v>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>195.1234416634805</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
@@ -25594,13 +25594,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
-        <v>193.8760457417114</v>
+        <v>193.4517821243685</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
@@ -25636,7 +25636,7 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>21.03597819208977</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
@@ -25645,10 +25645,10 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>114.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>136.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
@@ -25664,7 +25664,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>42.52409476750597</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
@@ -25688,7 +25688,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25712,28 +25712,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>183.5794145025583</v>
       </c>
       <c r="U42" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25788,7 +25788,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
         <v>177.2933913771695</v>
@@ -25809,10 +25809,10 @@
         <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y43" t="n">
-        <v>171.5597290184211</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350372.4996985703</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350372.4996985703</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350372.4996985704</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352018.7110648652</v>
+        <v>351692.9620346291</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557794</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506958.3588577136</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557795</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506958.3588577134</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488167.0194589256</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488167.0194589258</v>
+        <v>506968.6860557795</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488167.0194589258</v>
+        <v>506968.6860557797</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486721.531812865</v>
+        <v>487028.1657216359</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>64504.44331886783</v>
+      </c>
+      <c r="C2" t="n">
+        <v>64504.44331886783</v>
+      </c>
+      <c r="D2" t="n">
         <v>64504.44331886782</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64504.44331886782</v>
       </c>
-      <c r="D2" t="n">
-        <v>68921.32712272138</v>
-      </c>
-      <c r="E2" t="n">
-        <v>68921.32712272141</v>
-      </c>
       <c r="F2" t="n">
-        <v>68921.32712272141</v>
+        <v>64504.44331886783</v>
       </c>
       <c r="G2" t="n">
-        <v>69244.84892577637</v>
+        <v>69180.83107499292</v>
       </c>
       <c r="H2" t="n">
-        <v>99694.37396548246</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="I2" t="n">
-        <v>99694.37396548249</v>
+        <v>99696.40351879937</v>
       </c>
       <c r="J2" t="n">
-        <v>99694.37396548247</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="K2" t="n">
-        <v>99694.37396548242</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="L2" t="n">
-        <v>96001.40468548248</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="M2" t="n">
-        <v>96001.40468548248</v>
+        <v>99696.40351879939</v>
       </c>
       <c r="N2" t="n">
-        <v>96001.40468548251</v>
+        <v>99696.4035187994</v>
       </c>
       <c r="O2" t="n">
-        <v>95717.33012548246</v>
+        <v>95777.59137569282</v>
       </c>
       <c r="P2" t="n">
         <v>64504.44331886782</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>7562.01207347375</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16126.11082971696</v>
+        <v>18071.29444042431</v>
       </c>
       <c r="C4" t="n">
-        <v>16126.11082971696</v>
+        <v>18071.29444042431</v>
       </c>
       <c r="D4" t="n">
-        <v>17275.28476093078</v>
+        <v>18071.29444042431</v>
       </c>
       <c r="E4" t="n">
-        <v>17275.28476093077</v>
+        <v>18071.29444042431</v>
       </c>
       <c r="F4" t="n">
-        <v>17275.28476093077</v>
+        <v>18071.29444042431</v>
       </c>
       <c r="G4" t="n">
-        <v>17359.45786549053</v>
+        <v>19431.86900355542</v>
       </c>
       <c r="H4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="I4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100991</v>
       </c>
       <c r="J4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="K4" t="n">
-        <v>25281.74016844437</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="L4" t="n">
-        <v>24320.91253208073</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="M4" t="n">
-        <v>24320.91253208073</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="N4" t="n">
-        <v>24320.91253208073</v>
+        <v>28310.24133100992</v>
       </c>
       <c r="O4" t="n">
-        <v>24247.00271389891</v>
+        <v>27170.08007885187</v>
       </c>
       <c r="P4" t="n">
-        <v>16126.11082971696</v>
+        <v>18071.29444042431</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915087</v>
+        <v>12805.54887844352</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915087</v>
+        <v>12805.54887844352</v>
       </c>
       <c r="D6" t="n">
-        <v>8361.262361790614</v>
+        <v>12805.54887844351</v>
       </c>
       <c r="E6" t="n">
-        <v>50065.24236179064</v>
+        <v>46433.14887844351</v>
       </c>
       <c r="F6" t="n">
-        <v>50065.24236179064</v>
+        <v>46433.14887844352</v>
       </c>
       <c r="G6" t="n">
-        <v>49634.82106028585</v>
+        <v>40509.47646213652</v>
       </c>
       <c r="H6" t="n">
-        <v>2290.51679703809</v>
+        <v>-851.2937183038703</v>
       </c>
       <c r="I6" t="n">
-        <v>59759.83379703811</v>
+        <v>56732.49342402778</v>
       </c>
       <c r="J6" t="n">
-        <v>59759.83379703811</v>
+        <v>56732.49342402781</v>
       </c>
       <c r="K6" t="n">
-        <v>59759.83379703805</v>
+        <v>56732.49342402779</v>
       </c>
       <c r="L6" t="n">
-        <v>58608.49215340175</v>
+        <v>56732.49342402781</v>
       </c>
       <c r="M6" t="n">
-        <v>58608.49215340175</v>
+        <v>56732.49342402779</v>
       </c>
       <c r="N6" t="n">
-        <v>58608.49215340178</v>
+        <v>56732.49342402781</v>
       </c>
       <c r="O6" t="n">
-        <v>58519.92741158355</v>
+        <v>55631.3160689065</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>46433.14887844351</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -35097,13 +35097,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35170,10 +35170,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -35182,10 +35182,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.00000000000018</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,16 +35325,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35404,19 +35404,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,16 +35562,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35647,19 +35647,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,16 +35723,16 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36048,7 +36048,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O20" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
         <v>90.5657124162131</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>169.9091475161414</v>
       </c>
       <c r="P21" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>217.6787513871916</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36525,7 +36525,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,22 +36589,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="O27" t="n">
-        <v>239.9766607390413</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,25 +36826,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>226.3927858636067</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,16 +36984,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O32" t="n">
         <v>150.7019698410586</v>
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>9.59381962508408</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
         <v>70.09551364982758</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37303,16 +37303,16 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>215</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N36" t="n">
-        <v>206.3131313131313</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37537,22 +37537,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>110.2009720493048</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>104.0555615261842</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
-        <v>77.13683479509021</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37777,16 +37777,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>37.01765175063403</v>
       </c>
       <c r="N42" t="n">
-        <v>36.18626648028521</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
